--- a/VerveStacks_IND_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{345C0148-208A-4E68-91BB-170A9A4ED7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F736AD15-793B-4C1B-B09F-378757AA1100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1962,7 +1962,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A84F83-0EA3-4D2E-9252-29B138F4F03A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96671B2A-D7AD-4F70-8C0F-5B698FE7F7D8}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2019,7 +2019,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25DD6F80-EC54-4FC1-A5B0-23CEEEC25922}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A386B2F3-F57F-4E78-AC73-C81474437624}">
   <dimension ref="B9:O88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4265,7 +4265,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECCF794E-D663-472A-9806-2BE3F29CE671}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE17EC28-EFAB-4D55-AC45-67A47FB8F21B}">
   <dimension ref="B9:T179"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9299,7 +9299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D29FD7-B23B-461B-BB12-964B6903CAB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ECBB72C-5A86-4BD2-9152-3027673E1DE0}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9343,7 +9343,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B24BD1F-D344-43CB-ACA0-D9E6724B0A51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C908CC9-EFAD-49E9-AB24-2A73DE32E2B6}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9392,7 +9392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D62ED5-ED11-46A3-A107-6E6D289B3661}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7B95AA-FD76-4A2A-A63C-AC07C4FCC6E6}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9430,7 +9430,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E2973FA-9F3C-4390-9A93-8B7E12435C27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5B09BFB-5A67-4655-9204-D2C1A733B0AB}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9490,7 +9490,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.42094166666666671</v>
+        <v>0.4209416666666666</v>
       </c>
       <c r="E13" t="s">
         <v>405</v>
@@ -9504,7 +9504,7 @@
         <v>37</v>
       </c>
       <c r="D14">
-        <v>0.41899166666666665</v>
+        <v>0.41899166666666671</v>
       </c>
       <c r="E14" t="s">
         <v>405</v>
@@ -9546,7 +9546,7 @@
         <v>37</v>
       </c>
       <c r="D17">
-        <v>0.35627500000000006</v>
+        <v>0.35627499999999995</v>
       </c>
       <c r="E17" t="s">
         <v>405</v>
@@ -9616,7 +9616,7 @@
         <v>37</v>
       </c>
       <c r="D22">
-        <v>0.31999166666666673</v>
+        <v>0.31999166666666667</v>
       </c>
       <c r="E22" t="s">
         <v>405</v>
@@ -9658,7 +9658,7 @@
         <v>37</v>
       </c>
       <c r="D25">
-        <v>0.36420833333333341</v>
+        <v>0.3642083333333333</v>
       </c>
       <c r="E25" t="s">
         <v>405</v>
@@ -9700,7 +9700,7 @@
         <v>37</v>
       </c>
       <c r="D28">
-        <v>0.41515000000000007</v>
+        <v>0.41514999999999996</v>
       </c>
       <c r="E28" t="s">
         <v>405</v>
@@ -9714,7 +9714,7 @@
         <v>37</v>
       </c>
       <c r="D29">
-        <v>0.43407500000000004</v>
+        <v>0.43407499999999999</v>
       </c>
       <c r="E29" t="s">
         <v>405</v>
@@ -9742,7 +9742,7 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>0.41417499999999996</v>
+        <v>0.41417500000000002</v>
       </c>
       <c r="E31" t="s">
         <v>405</v>
@@ -9756,7 +9756,7 @@
         <v>37</v>
       </c>
       <c r="D32">
-        <v>0.422925</v>
+        <v>0.42292499999999994</v>
       </c>
       <c r="E32" t="s">
         <v>405</v>
@@ -9784,7 +9784,7 @@
         <v>37</v>
       </c>
       <c r="D34">
-        <v>0.36141666666666672</v>
+        <v>0.36141666666666666</v>
       </c>
       <c r="E34" t="s">
         <v>405</v>
